--- a/Data/TestData/TM_CM_Master.xlsx
+++ b/Data/TestData/TM_CM_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D26FEE-A9EF-4505-B691-16EB49F461D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14474B4B-EFEB-4664-AE91-945D502973D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="210" windowWidth="8520" windowHeight="10605" xr2:uid="{A6D9F5E8-45DA-470B-9D80-EDC43BD3438A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{A6D9F5E8-45DA-470B-9D80-EDC43BD3438A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Data/TestData/TM_CM_Master.xlsx
+++ b/Data/TestData/TM_CM_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14474B4B-EFEB-4664-AE91-945D502973D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3196E7-B4A9-431C-9ABD-67027D04D313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{A6D9F5E8-45DA-470B-9D80-EDC43BD3438A}"/>
   </bookViews>

--- a/Data/TestData/TM_CM_Master.xlsx
+++ b/Data/TestData/TM_CM_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3196E7-B4A9-431C-9ABD-67027D04D313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F940934-C385-41B4-8A5A-085DD074FB85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{A6D9F5E8-45DA-470B-9D80-EDC43BD3438A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" xr2:uid="{A6D9F5E8-45DA-470B-9D80-EDC43BD3438A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,23 +57,23 @@
     <t>BMOPT5647A</t>
   </si>
   <si>
-    <t>c10092042</t>
-  </si>
-  <si>
-    <t>BMOPT4884E</t>
-  </si>
-  <si>
-    <t>CMa10942</t>
-  </si>
-  <si>
-    <t>TM092027</t>
+    <t>BMOPT4884H</t>
+  </si>
+  <si>
+    <t>TM242028</t>
+  </si>
+  <si>
+    <t>c10092026</t>
+  </si>
+  <si>
+    <t>CMa12026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,6 +98,10 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -116,19 +120,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{2DE2F825-3627-40EC-B8D7-8C37C8CB2505}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{585EB2A7-65E0-48FB-BA33-93118AFEE059}"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -552,22 +559,22 @@
         <v>11</v>
       </c>
       <c r="D2" s="3">
-        <v>400920251732</v>
+        <v>24032026</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
